--- a/从零开始学Slots/从零开始学Slots-13-基础篇-Hold&Spin.xlsx
+++ b/从零开始学Slots/从零开始学Slots-13-基础篇-Hold&Spin.xlsx
@@ -6151,6 +6151,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:N145" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -6694,5 +6697,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:M65" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/从零开始学Slots/从零开始学Slots-13-基础篇-Hold&Spin.xlsx
+++ b/从零开始学Slots/从零开始学Slots-13-基础篇-Hold&Spin.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="184">
   <si>
     <r>
       <rPr>
@@ -5166,7 +5166,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5273,6 +5273,10 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -6312,8 +6316,8 @@
       <c r="A14" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="B14" s="16" t="s">
-        <v>132</v>
+      <c r="B14" s="27">
+        <v>20</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>133</v>
@@ -6326,8 +6330,8 @@
       <c r="A15" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="B15" s="16" t="s">
-        <v>136</v>
+      <c r="B15" s="27">
+        <v>25</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>129</v>
